--- a/src/assets/template/Birthday.xlsx
+++ b/src/assets/template/Birthday.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angular-Project\birthday-reminder\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>SubRelation</t>
+  </si>
+  <si>
+    <t>Contact</t>
   </si>
 </sst>
 </file>
@@ -84,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin">
@@ -128,30 +131,15 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -479,1354 +467,1239 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
-      <c r="B2" s="5"/>
-      <c r="G2" s="6"/>
+      <c r="B2" s="4"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3">
-      <c r="B3" s="5"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="4"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4">
-      <c r="B4" s="5"/>
-      <c r="G4" s="6"/>
+      <c r="B4" s="4"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5">
-      <c r="B5" s="5"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="4"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6">
-      <c r="B6" s="5"/>
-      <c r="G6" s="6"/>
+      <c r="B6" s="4"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7">
-      <c r="C7" s="5"/>
-      <c r="G7" s="6"/>
+      <c r="C7" s="4"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8">
-      <c r="C8" s="5"/>
-      <c r="G8" s="6"/>
+      <c r="C8" s="4"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9">
-      <c r="B9" s="5"/>
-      <c r="G9" s="6"/>
+      <c r="B9" s="4"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10">
-      <c r="B10" s="5"/>
-      <c r="G10" s="6"/>
+      <c r="B10" s="4"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11">
-      <c r="B11" s="5"/>
-      <c r="G11" s="6"/>
+      <c r="B11" s="4"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12">
-      <c r="B12" s="5"/>
-      <c r="G12" s="6"/>
+      <c r="B12" s="4"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13">
-      <c r="B13" s="5"/>
-      <c r="G13" s="6"/>
+      <c r="B13" s="4"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14">
-      <c r="C14" s="5"/>
-      <c r="G14" s="6"/>
+      <c r="C14" s="4"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15">
-      <c r="C15" s="5"/>
-      <c r="G15" s="6"/>
+      <c r="C15" s="4"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16">
-      <c r="B16" s="5"/>
-      <c r="G16" s="6"/>
+      <c r="B16" s="4"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17">
-      <c r="B17" s="5"/>
-      <c r="G17" s="6"/>
+      <c r="B17" s="4"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18">
-      <c r="B18" s="5"/>
-      <c r="G18" s="6"/>
+      <c r="B18" s="4"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19">
-      <c r="B19" s="5"/>
-      <c r="G19" s="6"/>
+      <c r="B19" s="4"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20">
-      <c r="C20" s="5"/>
-      <c r="G20" s="6"/>
+      <c r="C20" s="4"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21">
-      <c r="C21" s="5"/>
-      <c r="G21" s="6"/>
+      <c r="C21" s="4"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22">
-      <c r="C22" s="5"/>
-      <c r="G22" s="6"/>
+      <c r="C22" s="4"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23">
-      <c r="B23" s="5"/>
-      <c r="G23" s="6"/>
+      <c r="B23" s="4"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="24">
-      <c r="C24" s="5"/>
-      <c r="G24" s="6"/>
+      <c r="C24" s="4"/>
+      <c r="G24" s="5"/>
     </row>
     <row r="25">
-      <c r="B25" s="5"/>
-      <c r="G25" s="6"/>
+      <c r="B25" s="4"/>
+      <c r="G25" s="5"/>
     </row>
     <row r="26">
-      <c r="C26" s="5"/>
-      <c r="G26" s="6"/>
+      <c r="C26" s="4"/>
+      <c r="G26" s="5"/>
     </row>
     <row r="27">
-      <c r="B27" s="5"/>
-      <c r="G27" s="6"/>
+      <c r="B27" s="4"/>
+      <c r="G27" s="5"/>
     </row>
     <row r="28">
-      <c r="C28" s="5"/>
-      <c r="G28" s="6"/>
+      <c r="C28" s="4"/>
+      <c r="G28" s="5"/>
     </row>
     <row r="29">
-      <c r="B29" s="5"/>
-      <c r="G29" s="6"/>
+      <c r="B29" s="4"/>
+      <c r="G29" s="5"/>
     </row>
     <row r="30">
-      <c r="C30" s="5"/>
-      <c r="G30" s="6"/>
+      <c r="C30" s="4"/>
+      <c r="G30" s="5"/>
     </row>
     <row r="31">
-      <c r="B31" s="5"/>
-      <c r="G31" s="6"/>
+      <c r="B31" s="4"/>
+      <c r="G31" s="5"/>
     </row>
     <row r="32">
-      <c r="B32" s="5"/>
-      <c r="G32" s="6"/>
+      <c r="B32" s="4"/>
+      <c r="G32" s="5"/>
     </row>
     <row r="33">
-      <c r="C33" s="5"/>
-      <c r="G33" s="6"/>
+      <c r="C33" s="4"/>
+      <c r="G33" s="5"/>
     </row>
     <row r="34">
-      <c r="B34" s="5"/>
-      <c r="G34" s="6"/>
+      <c r="B34" s="4"/>
+      <c r="G34" s="5"/>
     </row>
     <row r="35">
-      <c r="B35" s="5"/>
-      <c r="G35" s="6"/>
+      <c r="B35" s="4"/>
+      <c r="G35" s="5"/>
     </row>
     <row r="36">
-      <c r="C36" s="5"/>
-      <c r="G36" s="6"/>
+      <c r="C36" s="4"/>
+      <c r="G36" s="5"/>
     </row>
     <row r="37">
-      <c r="C37" s="5"/>
-      <c r="G37" s="6"/>
+      <c r="C37" s="4"/>
+      <c r="G37" s="5"/>
     </row>
     <row r="38">
-      <c r="B38" s="5"/>
-      <c r="G38" s="6"/>
+      <c r="B38" s="4"/>
+      <c r="G38" s="5"/>
     </row>
     <row r="39">
-      <c r="B39" s="5"/>
-      <c r="G39" s="6"/>
+      <c r="B39" s="4"/>
+      <c r="G39" s="5"/>
     </row>
     <row r="40">
-      <c r="C40" s="5"/>
-      <c r="G40" s="6"/>
+      <c r="C40" s="4"/>
+      <c r="G40" s="5"/>
     </row>
     <row r="41">
-      <c r="C41" s="5"/>
-      <c r="G41" s="6"/>
+      <c r="C41" s="4"/>
+      <c r="G41" s="5"/>
     </row>
     <row r="42">
-      <c r="C42" s="5"/>
-      <c r="G42" s="6"/>
+      <c r="C42" s="4"/>
+      <c r="G42" s="5"/>
     </row>
     <row r="43">
-      <c r="B43" s="5"/>
-      <c r="G43" s="6"/>
+      <c r="B43" s="4"/>
+      <c r="G43" s="5"/>
     </row>
     <row r="44">
-      <c r="C44" s="5"/>
-      <c r="G44" s="6"/>
+      <c r="C44" s="4"/>
+      <c r="G44" s="5"/>
     </row>
     <row r="45">
-      <c r="C45" s="5"/>
-      <c r="G45" s="6"/>
+      <c r="C45" s="4"/>
+      <c r="G45" s="5"/>
     </row>
     <row r="46">
-      <c r="B46" s="5"/>
-      <c r="G46" s="6"/>
+      <c r="B46" s="4"/>
+      <c r="G46" s="5"/>
     </row>
     <row r="47">
-      <c r="C47" s="5"/>
-      <c r="G47" s="6"/>
+      <c r="C47" s="4"/>
+      <c r="G47" s="5"/>
     </row>
     <row r="48">
-      <c r="C48" s="5"/>
-      <c r="G48" s="6"/>
+      <c r="C48" s="4"/>
+      <c r="G48" s="5"/>
     </row>
     <row r="49">
-      <c r="C49" s="5"/>
-      <c r="G49" s="6"/>
+      <c r="C49" s="4"/>
+      <c r="G49" s="5"/>
     </row>
     <row r="50">
-      <c r="C50" s="5"/>
-      <c r="G50" s="6"/>
+      <c r="C50" s="4"/>
+      <c r="G50" s="5"/>
     </row>
     <row r="51">
-      <c r="B51" s="5"/>
-      <c r="G51" s="6"/>
+      <c r="B51" s="4"/>
+      <c r="G51" s="5"/>
     </row>
     <row r="52">
-      <c r="C52" s="5"/>
-      <c r="G52" s="6"/>
+      <c r="C52" s="4"/>
+      <c r="G52" s="5"/>
     </row>
     <row r="53">
-      <c r="C53" s="5"/>
-      <c r="G53" s="6"/>
+      <c r="C53" s="4"/>
+      <c r="G53" s="5"/>
     </row>
     <row r="54">
-      <c r="B54" s="5"/>
-      <c r="G54" s="6"/>
+      <c r="B54" s="4"/>
+      <c r="G54" s="5"/>
     </row>
     <row r="55">
-      <c r="C55" s="5"/>
-      <c r="G55" s="6"/>
+      <c r="C55" s="4"/>
+      <c r="G55" s="5"/>
     </row>
     <row r="56">
-      <c r="B56" s="5"/>
-      <c r="G56" s="6"/>
+      <c r="B56" s="4"/>
+      <c r="G56" s="5"/>
     </row>
     <row r="57">
-      <c r="C57" s="5"/>
-      <c r="G57" s="6"/>
+      <c r="C57" s="4"/>
+      <c r="G57" s="5"/>
     </row>
     <row r="58">
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="G58" s="6"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="G58" s="5"/>
     </row>
     <row r="59">
-      <c r="C59" s="5"/>
-      <c r="G59" s="6"/>
+      <c r="C59" s="4"/>
+      <c r="G59" s="5"/>
     </row>
     <row r="60">
-      <c r="B60" s="5"/>
-      <c r="G60" s="6"/>
+      <c r="B60" s="4"/>
+      <c r="G60" s="5"/>
     </row>
     <row r="61">
-      <c r="C61" s="5"/>
-      <c r="G61" s="6"/>
+      <c r="C61" s="4"/>
+      <c r="G61" s="5"/>
     </row>
     <row r="62">
-      <c r="C62" s="5"/>
-      <c r="G62" s="6"/>
+      <c r="C62" s="4"/>
+      <c r="G62" s="5"/>
     </row>
     <row r="63">
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="G63" s="6"/>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="G63" s="5"/>
     </row>
     <row r="64">
-      <c r="B64" s="5"/>
-      <c r="G64" s="6"/>
+      <c r="B64" s="4"/>
+      <c r="G64" s="5"/>
     </row>
     <row r="65">
-      <c r="B65" s="5"/>
-      <c r="G65" s="6"/>
+      <c r="B65" s="4"/>
+      <c r="G65" s="5"/>
     </row>
     <row r="66">
-      <c r="B66" s="5"/>
-      <c r="G66" s="6"/>
+      <c r="B66" s="4"/>
+      <c r="G66" s="5"/>
     </row>
     <row r="67">
-      <c r="B67" s="5"/>
-      <c r="G67" s="6"/>
+      <c r="B67" s="4"/>
+      <c r="G67" s="5"/>
     </row>
     <row r="68">
-      <c r="C68" s="5"/>
-      <c r="G68" s="6"/>
+      <c r="C68" s="4"/>
+      <c r="G68" s="5"/>
     </row>
     <row r="69">
-      <c r="B69" s="5"/>
-      <c r="G69" s="6"/>
+      <c r="B69" s="4"/>
+      <c r="G69" s="5"/>
     </row>
     <row r="70">
-      <c r="C70" s="5"/>
-      <c r="G70" s="6"/>
+      <c r="C70" s="4"/>
+      <c r="G70" s="5"/>
     </row>
     <row r="71">
-      <c r="C71" s="5"/>
-      <c r="G71" s="6"/>
+      <c r="C71" s="4"/>
+      <c r="G71" s="5"/>
     </row>
     <row r="72">
-      <c r="B72" s="5"/>
-      <c r="G72" s="6"/>
+      <c r="B72" s="4"/>
+      <c r="G72" s="5"/>
     </row>
     <row r="73">
-      <c r="B73" s="5"/>
-      <c r="G73" s="6"/>
+      <c r="B73" s="4"/>
+      <c r="G73" s="5"/>
     </row>
     <row r="74">
-      <c r="C74" s="5"/>
-      <c r="G74" s="6"/>
+      <c r="C74" s="4"/>
+      <c r="G74" s="5"/>
     </row>
     <row r="75">
-      <c r="C75" s="5"/>
-      <c r="G75" s="6"/>
+      <c r="C75" s="4"/>
+      <c r="G75" s="5"/>
     </row>
     <row r="76">
-      <c r="B76" s="5"/>
-      <c r="G76" s="6"/>
+      <c r="B76" s="4"/>
+      <c r="G76" s="5"/>
     </row>
     <row r="77">
-      <c r="B77" s="5"/>
-      <c r="G77" s="6"/>
+      <c r="B77" s="4"/>
+      <c r="G77" s="5"/>
     </row>
     <row r="78">
-      <c r="B78" s="5"/>
-      <c r="G78" s="6"/>
+      <c r="B78" s="4"/>
+      <c r="G78" s="5"/>
     </row>
     <row r="79">
-      <c r="C79" s="5"/>
-      <c r="G79" s="6"/>
+      <c r="C79" s="4"/>
+      <c r="G79" s="5"/>
     </row>
     <row r="80">
-      <c r="C80" s="5"/>
-      <c r="G80" s="6"/>
+      <c r="C80" s="4"/>
+      <c r="G80" s="5"/>
     </row>
     <row r="81">
-      <c r="C81" s="5"/>
-      <c r="G81" s="6"/>
+      <c r="C81" s="4"/>
+      <c r="G81" s="5"/>
     </row>
     <row r="82">
-      <c r="B82" s="5"/>
-      <c r="G82" s="6"/>
+      <c r="B82" s="4"/>
+      <c r="G82" s="5"/>
     </row>
     <row r="83">
-      <c r="C83" s="5"/>
-      <c r="G83" s="6"/>
+      <c r="C83" s="4"/>
+      <c r="G83" s="5"/>
     </row>
     <row r="84">
-      <c r="C84" s="5"/>
-      <c r="G84" s="6"/>
+      <c r="C84" s="4"/>
+      <c r="G84" s="5"/>
     </row>
     <row r="85">
-      <c r="C85" s="5"/>
-      <c r="G85" s="6"/>
+      <c r="C85" s="4"/>
+      <c r="G85" s="5"/>
     </row>
     <row r="86">
-      <c r="C86" s="5"/>
-      <c r="G86" s="6"/>
+      <c r="C86" s="4"/>
+      <c r="G86" s="5"/>
     </row>
     <row r="87">
-      <c r="C87" s="5"/>
-      <c r="G87" s="6"/>
+      <c r="C87" s="4"/>
+      <c r="G87" s="5"/>
     </row>
     <row r="88">
-      <c r="B88" s="5"/>
-      <c r="G88" s="6"/>
+      <c r="B88" s="4"/>
+      <c r="G88" s="5"/>
     </row>
     <row r="89">
-      <c r="B89" s="5"/>
-      <c r="G89" s="6"/>
+      <c r="B89" s="4"/>
+      <c r="G89" s="5"/>
     </row>
     <row r="90">
-      <c r="B90" s="5"/>
-      <c r="G90" s="6"/>
+      <c r="B90" s="4"/>
+      <c r="G90" s="5"/>
     </row>
     <row r="91">
-      <c r="B91" s="5"/>
-      <c r="G91" s="6"/>
+      <c r="B91" s="4"/>
+      <c r="G91" s="5"/>
     </row>
     <row r="92">
-      <c r="B92" s="5"/>
-      <c r="G92" s="6"/>
+      <c r="B92" s="4"/>
+      <c r="G92" s="5"/>
     </row>
     <row r="93">
-      <c r="B93" s="5"/>
-      <c r="G93" s="6"/>
+      <c r="B93" s="4"/>
+      <c r="G93" s="5"/>
     </row>
     <row r="94">
-      <c r="B94" s="5"/>
-      <c r="G94" s="6"/>
+      <c r="B94" s="4"/>
+      <c r="G94" s="5"/>
     </row>
     <row r="95">
-      <c r="B95" s="5"/>
-      <c r="G95" s="6"/>
+      <c r="B95" s="4"/>
+      <c r="G95" s="5"/>
     </row>
     <row r="96">
-      <c r="C96" s="5"/>
-      <c r="G96" s="6"/>
+      <c r="C96" s="4"/>
+      <c r="G96" s="5"/>
     </row>
     <row r="97">
-      <c r="B97" s="5"/>
-      <c r="G97" s="6"/>
+      <c r="B97" s="4"/>
+      <c r="G97" s="5"/>
     </row>
     <row r="98">
-      <c r="B98" s="5"/>
-      <c r="G98" s="6"/>
+      <c r="B98" s="4"/>
+      <c r="G98" s="5"/>
     </row>
     <row r="99">
-      <c r="B99" s="5"/>
-      <c r="G99" s="6"/>
+      <c r="B99" s="4"/>
+      <c r="G99" s="5"/>
     </row>
     <row r="100">
-      <c r="B100" s="5"/>
-      <c r="G100" s="6"/>
+      <c r="B100" s="4"/>
+      <c r="G100" s="5"/>
     </row>
     <row r="101">
-      <c r="B101" s="5"/>
-      <c r="G101" s="6"/>
+      <c r="B101" s="4"/>
+      <c r="G101" s="5"/>
     </row>
     <row r="102">
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="G102" s="6"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="G102" s="5"/>
     </row>
     <row r="103">
-      <c r="C103" s="5"/>
-      <c r="G103" s="6"/>
+      <c r="C103" s="4"/>
+      <c r="G103" s="5"/>
     </row>
     <row r="104">
-      <c r="C104" s="5"/>
-      <c r="G104" s="6"/>
+      <c r="C104" s="4"/>
+      <c r="G104" s="5"/>
     </row>
     <row r="105">
-      <c r="B105" s="5"/>
-      <c r="G105" s="6"/>
+      <c r="B105" s="4"/>
+      <c r="G105" s="5"/>
     </row>
     <row r="106">
-      <c r="B106" s="5"/>
-      <c r="G106" s="6"/>
+      <c r="B106" s="4"/>
+      <c r="G106" s="5"/>
     </row>
     <row r="107">
-      <c r="C107" s="5"/>
-      <c r="G107" s="6"/>
+      <c r="C107" s="4"/>
+      <c r="G107" s="5"/>
     </row>
     <row r="108">
-      <c r="B108" s="5"/>
-      <c r="G108" s="6"/>
+      <c r="B108" s="4"/>
+      <c r="G108" s="5"/>
     </row>
     <row r="109">
-      <c r="B109" s="5"/>
-      <c r="G109" s="6"/>
+      <c r="B109" s="4"/>
+      <c r="G109" s="5"/>
     </row>
     <row r="110">
-      <c r="B110" s="5"/>
-      <c r="G110" s="6"/>
+      <c r="B110" s="4"/>
+      <c r="G110" s="5"/>
     </row>
     <row r="111">
-      <c r="C111" s="5"/>
-      <c r="G111" s="6"/>
+      <c r="C111" s="4"/>
+      <c r="G111" s="5"/>
     </row>
     <row r="112">
-      <c r="B112" s="5"/>
-      <c r="G112" s="6"/>
+      <c r="B112" s="4"/>
+      <c r="G112" s="5"/>
     </row>
     <row r="113">
-      <c r="C113" s="5"/>
-      <c r="G113" s="6"/>
+      <c r="C113" s="4"/>
+      <c r="G113" s="5"/>
     </row>
     <row r="114">
-      <c r="C114" s="5"/>
-      <c r="G114" s="6"/>
+      <c r="C114" s="4"/>
+      <c r="G114" s="5"/>
     </row>
     <row r="115">
-      <c r="C115" s="5"/>
-      <c r="G115" s="6"/>
+      <c r="C115" s="4"/>
+      <c r="G115" s="5"/>
     </row>
     <row r="116">
-      <c r="B116" s="5"/>
-      <c r="G116" s="6"/>
+      <c r="B116" s="4"/>
+      <c r="G116" s="5"/>
     </row>
     <row r="117">
-      <c r="C117" s="5"/>
-      <c r="G117" s="6"/>
+      <c r="C117" s="4"/>
+      <c r="G117" s="5"/>
     </row>
     <row r="118">
-      <c r="C118" s="5"/>
-      <c r="G118" s="6"/>
+      <c r="C118" s="4"/>
+      <c r="G118" s="5"/>
     </row>
     <row r="119">
-      <c r="B119" s="5"/>
-      <c r="G119" s="6"/>
+      <c r="B119" s="4"/>
+      <c r="G119" s="5"/>
     </row>
     <row r="120">
-      <c r="B120" s="5"/>
-      <c r="G120" s="6"/>
+      <c r="B120" s="4"/>
+      <c r="G120" s="5"/>
     </row>
     <row r="121">
-      <c r="C121" s="5"/>
-      <c r="G121" s="6"/>
+      <c r="C121" s="4"/>
+      <c r="G121" s="5"/>
     </row>
     <row r="122">
-      <c r="C122" s="5"/>
-      <c r="G122" s="6"/>
+      <c r="C122" s="4"/>
+      <c r="G122" s="5"/>
     </row>
     <row r="123">
-      <c r="C123" s="5"/>
-      <c r="G123" s="6"/>
+      <c r="C123" s="4"/>
+      <c r="G123" s="5"/>
     </row>
     <row r="124">
-      <c r="C124" s="5"/>
-      <c r="G124" s="6"/>
+      <c r="C124" s="4"/>
+      <c r="G124" s="5"/>
     </row>
     <row r="125">
-      <c r="C125" s="5"/>
-      <c r="G125" s="6"/>
+      <c r="C125" s="4"/>
+      <c r="G125" s="5"/>
     </row>
     <row r="126">
-      <c r="C126" s="5"/>
-      <c r="G126" s="6"/>
+      <c r="C126" s="4"/>
+      <c r="G126" s="5"/>
     </row>
     <row r="127">
-      <c r="B127" s="5"/>
-      <c r="G127" s="6"/>
+      <c r="B127" s="4"/>
+      <c r="G127" s="5"/>
     </row>
     <row r="128">
-      <c r="C128" s="5"/>
-      <c r="G128" s="6"/>
+      <c r="C128" s="4"/>
+      <c r="G128" s="5"/>
     </row>
     <row r="129">
-      <c r="C129" s="5"/>
-      <c r="G129" s="6"/>
+      <c r="C129" s="4"/>
+      <c r="G129" s="5"/>
     </row>
     <row r="130">
-      <c r="C130" s="5"/>
-      <c r="G130" s="6"/>
+      <c r="C130" s="4"/>
+      <c r="G130" s="5"/>
     </row>
     <row r="131">
-      <c r="C131" s="5"/>
-      <c r="G131" s="6"/>
+      <c r="C131" s="4"/>
+      <c r="G131" s="5"/>
     </row>
     <row r="132">
-      <c r="C132" s="5"/>
-      <c r="G132" s="6"/>
+      <c r="C132" s="4"/>
+      <c r="G132" s="5"/>
     </row>
     <row r="133">
-      <c r="B133" s="5"/>
-      <c r="G133" s="6"/>
+      <c r="B133" s="4"/>
+      <c r="G133" s="5"/>
     </row>
     <row r="134">
-      <c r="C134" s="5"/>
-      <c r="G134" s="6"/>
+      <c r="C134" s="4"/>
+      <c r="G134" s="5"/>
     </row>
     <row r="135">
-      <c r="C135" s="5"/>
-      <c r="G135" s="6"/>
+      <c r="C135" s="4"/>
+      <c r="G135" s="5"/>
     </row>
     <row r="136">
-      <c r="C136" s="5"/>
-      <c r="G136" s="6"/>
+      <c r="C136" s="4"/>
+      <c r="G136" s="5"/>
     </row>
     <row r="137">
-      <c r="B137" s="5"/>
-      <c r="G137" s="6"/>
+      <c r="B137" s="4"/>
+      <c r="G137" s="5"/>
     </row>
     <row r="138">
-      <c r="B138" s="5"/>
-      <c r="G138" s="6"/>
+      <c r="B138" s="4"/>
+      <c r="G138" s="5"/>
     </row>
     <row r="139">
-      <c r="C139" s="5"/>
-      <c r="G139" s="6"/>
+      <c r="C139" s="4"/>
+      <c r="G139" s="5"/>
     </row>
     <row r="140">
-      <c r="B140" s="5"/>
-      <c r="G140" s="6"/>
+      <c r="B140" s="4"/>
+      <c r="G140" s="5"/>
     </row>
     <row r="141">
-      <c r="B141" s="5"/>
-      <c r="G141" s="6"/>
+      <c r="B141" s="4"/>
+      <c r="G141" s="5"/>
     </row>
     <row r="142">
-      <c r="B142" s="5"/>
-      <c r="G142" s="6"/>
+      <c r="B142" s="4"/>
+      <c r="G142" s="5"/>
     </row>
     <row r="143">
-      <c r="B143" s="5"/>
-      <c r="G143" s="6"/>
+      <c r="B143" s="4"/>
+      <c r="G143" s="5"/>
     </row>
     <row r="144">
-      <c r="B144" s="5"/>
-      <c r="G144" s="6"/>
+      <c r="B144" s="4"/>
+      <c r="G144" s="5"/>
     </row>
     <row r="145">
-      <c r="B145" s="5"/>
-      <c r="G145" s="6"/>
+      <c r="B145" s="4"/>
+      <c r="G145" s="5"/>
     </row>
     <row r="146">
-      <c r="C146" s="5"/>
-      <c r="G146" s="6"/>
+      <c r="C146" s="4"/>
+      <c r="G146" s="5"/>
     </row>
     <row r="147">
-      <c r="C147" s="5"/>
-      <c r="G147" s="6"/>
+      <c r="C147" s="4"/>
+      <c r="G147" s="5"/>
     </row>
     <row r="148">
-      <c r="C148" s="5"/>
-      <c r="G148" s="6"/>
+      <c r="C148" s="4"/>
+      <c r="G148" s="5"/>
     </row>
     <row r="149">
-      <c r="B149" s="5"/>
-      <c r="G149" s="6"/>
+      <c r="B149" s="4"/>
+      <c r="G149" s="5"/>
     </row>
     <row r="150">
-      <c r="C150" s="5"/>
-      <c r="G150" s="6"/>
+      <c r="C150" s="4"/>
+      <c r="G150" s="5"/>
     </row>
     <row r="151">
-      <c r="C151" s="5"/>
-      <c r="G151" s="6"/>
+      <c r="C151" s="4"/>
+      <c r="G151" s="5"/>
     </row>
     <row r="152">
-      <c r="B152" s="5"/>
-      <c r="G152" s="6"/>
+      <c r="B152" s="4"/>
+      <c r="G152" s="5"/>
     </row>
     <row r="153">
-      <c r="B153" s="5"/>
-      <c r="G153" s="6"/>
+      <c r="B153" s="4"/>
+      <c r="G153" s="5"/>
     </row>
     <row r="154">
-      <c r="C154" s="5"/>
-      <c r="G154" s="6"/>
+      <c r="C154" s="4"/>
+      <c r="G154" s="5"/>
     </row>
     <row r="155">
-      <c r="B155" s="5"/>
-      <c r="G155" s="6"/>
+      <c r="B155" s="4"/>
+      <c r="G155" s="5"/>
     </row>
     <row r="156">
-      <c r="B156" s="5"/>
-      <c r="G156" s="6"/>
+      <c r="B156" s="4"/>
+      <c r="G156" s="5"/>
     </row>
     <row r="157">
-      <c r="B157" s="5"/>
-      <c r="G157" s="6"/>
+      <c r="B157" s="4"/>
+      <c r="G157" s="5"/>
     </row>
     <row r="158">
-      <c r="B158" s="5"/>
-      <c r="G158" s="6"/>
+      <c r="B158" s="4"/>
+      <c r="G158" s="5"/>
     </row>
     <row r="159">
-      <c r="C159" s="5"/>
-      <c r="G159" s="6"/>
+      <c r="C159" s="4"/>
+      <c r="G159" s="5"/>
     </row>
     <row r="160">
-      <c r="B160" s="5"/>
-      <c r="G160" s="6"/>
+      <c r="B160" s="4"/>
+      <c r="G160" s="5"/>
     </row>
     <row r="161">
-      <c r="B161" s="5"/>
-      <c r="G161" s="6"/>
+      <c r="B161" s="4"/>
+      <c r="G161" s="5"/>
     </row>
     <row r="162">
-      <c r="C162" s="5"/>
-      <c r="G162" s="6"/>
+      <c r="C162" s="4"/>
+      <c r="G162" s="5"/>
     </row>
     <row r="163">
-      <c r="C163" s="5"/>
-      <c r="G163" s="6"/>
+      <c r="C163" s="4"/>
+      <c r="G163" s="5"/>
     </row>
     <row r="164">
-      <c r="C164" s="5"/>
-      <c r="G164" s="6"/>
+      <c r="C164" s="4"/>
+      <c r="G164" s="5"/>
     </row>
     <row r="165">
-      <c r="B165" s="5"/>
-      <c r="G165" s="6"/>
+      <c r="B165" s="4"/>
+      <c r="G165" s="5"/>
     </row>
     <row r="166">
-      <c r="B166" s="5"/>
-      <c r="G166" s="6"/>
+      <c r="B166" s="4"/>
+      <c r="G166" s="5"/>
     </row>
     <row r="167">
-      <c r="C167" s="5"/>
-      <c r="G167" s="6"/>
+      <c r="C167" s="4"/>
+      <c r="G167" s="5"/>
     </row>
     <row r="168">
-      <c r="B168" s="5"/>
-      <c r="G168" s="6"/>
+      <c r="B168" s="4"/>
+      <c r="G168" s="5"/>
     </row>
     <row r="169">
-      <c r="B169" s="5"/>
-      <c r="G169" s="6"/>
+      <c r="B169" s="4"/>
+      <c r="G169" s="5"/>
     </row>
     <row r="170">
-      <c r="C170" s="5"/>
-      <c r="G170" s="6"/>
+      <c r="C170" s="4"/>
+      <c r="G170" s="5"/>
     </row>
     <row r="171">
-      <c r="B171" s="5"/>
-      <c r="G171" s="6"/>
+      <c r="B171" s="4"/>
+      <c r="G171" s="5"/>
     </row>
     <row r="172">
-      <c r="C172" s="5"/>
-      <c r="G172" s="6"/>
+      <c r="C172" s="4"/>
+      <c r="G172" s="5"/>
     </row>
     <row r="173">
-      <c r="C173" s="5"/>
-      <c r="G173" s="6"/>
+      <c r="C173" s="4"/>
+      <c r="G173" s="5"/>
     </row>
     <row r="174">
-      <c r="C174" s="5"/>
-      <c r="G174" s="6"/>
+      <c r="C174" s="4"/>
+      <c r="G174" s="5"/>
     </row>
     <row r="175">
-      <c r="B175" s="5"/>
-      <c r="G175" s="6"/>
+      <c r="B175" s="4"/>
+      <c r="G175" s="5"/>
     </row>
     <row r="176">
-      <c r="B176" s="5"/>
-      <c r="G176" s="6"/>
+      <c r="B176" s="4"/>
+      <c r="G176" s="5"/>
     </row>
     <row r="177">
-      <c r="C177" s="5"/>
-      <c r="G177" s="6"/>
+      <c r="C177" s="4"/>
+      <c r="G177" s="5"/>
     </row>
     <row r="178">
-      <c r="C178" s="5"/>
-      <c r="G178" s="6"/>
+      <c r="C178" s="4"/>
+      <c r="G178" s="5"/>
     </row>
     <row r="179">
-      <c r="B179" s="5"/>
-      <c r="G179" s="6"/>
+      <c r="B179" s="4"/>
+      <c r="G179" s="5"/>
     </row>
     <row r="180">
-      <c r="B180" s="5"/>
-      <c r="G180" s="6"/>
+      <c r="B180" s="4"/>
+      <c r="G180" s="5"/>
     </row>
     <row r="181">
-      <c r="B181" s="5"/>
-      <c r="G181" s="6"/>
+      <c r="B181" s="4"/>
+      <c r="G181" s="5"/>
     </row>
     <row r="182">
-      <c r="B182" s="5"/>
-      <c r="G182" s="6"/>
+      <c r="B182" s="4"/>
+      <c r="G182" s="5"/>
     </row>
     <row r="183">
-      <c r="B183" s="5"/>
-      <c r="G183" s="6"/>
+      <c r="B183" s="4"/>
+      <c r="G183" s="5"/>
     </row>
     <row r="184">
-      <c r="B184" s="5"/>
-      <c r="G184" s="6"/>
+      <c r="B184" s="4"/>
+      <c r="G184" s="5"/>
     </row>
     <row r="185">
-      <c r="B185" s="5"/>
-      <c r="G185" s="6"/>
+      <c r="B185" s="4"/>
+      <c r="G185" s="5"/>
     </row>
     <row r="186">
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
-      <c r="G186" s="6"/>
+      <c r="B186" s="4"/>
+      <c r="C186" s="4"/>
+      <c r="G186" s="5"/>
     </row>
     <row r="187">
-      <c r="C187" s="5"/>
-      <c r="G187" s="6"/>
+      <c r="C187" s="4"/>
+      <c r="G187" s="5"/>
     </row>
     <row r="188">
-      <c r="B188" s="5"/>
-      <c r="G188" s="6"/>
+      <c r="B188" s="4"/>
+      <c r="G188" s="5"/>
     </row>
     <row r="189">
-      <c r="C189" s="5"/>
-      <c r="G189" s="6"/>
+      <c r="C189" s="4"/>
+      <c r="G189" s="5"/>
     </row>
     <row r="190">
-      <c r="B190" s="5"/>
-      <c r="G190" s="6"/>
+      <c r="B190" s="4"/>
+      <c r="G190" s="5"/>
     </row>
     <row r="191">
-      <c r="B191" s="5"/>
-      <c r="G191" s="6"/>
+      <c r="B191" s="4"/>
+      <c r="G191" s="5"/>
     </row>
     <row r="192">
-      <c r="B192" s="5"/>
-      <c r="G192" s="6"/>
+      <c r="B192" s="4"/>
+      <c r="G192" s="5"/>
     </row>
     <row r="193">
-      <c r="A193"/>
-      <c r="B193" s="5"/>
+      <c r="B193" s="4"/>
     </row>
     <row r="194">
-      <c r="A194"/>
-      <c r="B194" s="5"/>
+      <c r="B194" s="4"/>
     </row>
     <row r="195">
-      <c r="A195"/>
-      <c r="B195" s="5"/>
+      <c r="B195" s="4"/>
     </row>
     <row r="196">
-      <c r="A196"/>
-      <c r="B196" s="5"/>
+      <c r="B196" s="4"/>
     </row>
     <row r="197">
-      <c r="A197"/>
-      <c r="B197" s="5"/>
+      <c r="B197" s="4"/>
     </row>
     <row r="198">
-      <c r="A198"/>
-      <c r="B198" s="5"/>
+      <c r="B198" s="4"/>
     </row>
     <row r="199">
-      <c r="A199"/>
-      <c r="B199" s="5"/>
+      <c r="B199" s="4"/>
     </row>
     <row r="200">
-      <c r="A200"/>
-      <c r="B200" s="5"/>
+      <c r="B200" s="4"/>
     </row>
     <row r="201">
-      <c r="A201"/>
-      <c r="B201" s="5"/>
+      <c r="B201" s="4"/>
     </row>
     <row r="202">
-      <c r="A202"/>
-      <c r="B202" s="5"/>
+      <c r="B202" s="4"/>
     </row>
     <row r="203">
-      <c r="A203"/>
-      <c r="B203" s="5"/>
+      <c r="B203" s="4"/>
     </row>
     <row r="204">
-      <c r="A204"/>
-      <c r="B204" s="5"/>
+      <c r="B204" s="4"/>
     </row>
     <row r="205">
-      <c r="A205"/>
-      <c r="B205" s="5"/>
+      <c r="B205" s="4"/>
     </row>
     <row r="206">
-      <c r="C206" s="5"/>
+      <c r="C206" s="4"/>
     </row>
     <row r="207">
-      <c r="C207" s="5"/>
+      <c r="C207" s="4"/>
     </row>
     <row r="208">
-      <c r="A208"/>
-      <c r="B208" s="5"/>
+      <c r="B208" s="4"/>
     </row>
     <row r="209">
-      <c r="C209" s="5"/>
+      <c r="C209" s="4"/>
     </row>
     <row r="210">
-      <c r="C210" s="5"/>
+      <c r="C210" s="4"/>
     </row>
     <row r="211">
-      <c r="C211" s="5"/>
+      <c r="C211" s="4"/>
     </row>
     <row r="212">
-      <c r="C212" s="5"/>
+      <c r="C212" s="4"/>
     </row>
     <row r="213">
-      <c r="A213"/>
-      <c r="B213" s="5"/>
+      <c r="B213" s="4"/>
     </row>
     <row r="214">
-      <c r="A214"/>
-      <c r="B214" s="5"/>
+      <c r="B214" s="4"/>
     </row>
     <row r="215">
-      <c r="C215" s="5"/>
+      <c r="C215" s="4"/>
     </row>
     <row r="216">
-      <c r="A216"/>
-      <c r="C216" s="5"/>
-      <c r="D216"/>
-      <c r="E216"/>
+      <c r="C216" s="4"/>
     </row>
     <row r="217">
-      <c r="C217" s="5"/>
+      <c r="C217" s="4"/>
     </row>
     <row r="218">
-      <c r="A218"/>
-      <c r="B218" s="5"/>
+      <c r="B218" s="4"/>
     </row>
     <row r="219">
-      <c r="A219"/>
-      <c r="B219" s="5"/>
+      <c r="B219" s="4"/>
     </row>
     <row r="220">
-      <c r="A220"/>
-      <c r="B220" s="5"/>
-      <c r="D220"/>
-      <c r="E220"/>
+      <c r="B220" s="4"/>
     </row>
     <row r="221">
-      <c r="A221"/>
-      <c r="B221" s="5"/>
+      <c r="B221" s="4"/>
     </row>
     <row r="222">
-      <c r="A222"/>
-      <c r="B222" s="5"/>
+      <c r="B222" s="4"/>
     </row>
     <row r="223">
-      <c r="A223"/>
-      <c r="B223" s="5"/>
+      <c r="B223" s="4"/>
     </row>
     <row r="224">
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
+      <c r="B224" s="4"/>
+      <c r="C224" s="4"/>
     </row>
     <row r="225">
-      <c r="A225"/>
-      <c r="B225" s="5"/>
+      <c r="B225" s="4"/>
     </row>
     <row r="226">
-      <c r="A226"/>
-      <c r="B226" s="5"/>
+      <c r="B226" s="4"/>
     </row>
     <row r="227">
-      <c r="A227"/>
-      <c r="B227" s="5"/>
+      <c r="B227" s="4"/>
     </row>
     <row r="228">
-      <c r="A228"/>
-      <c r="B228" s="5"/>
+      <c r="B228" s="4"/>
     </row>
     <row r="229">
-      <c r="B229" s="5"/>
-      <c r="C229" s="5"/>
+      <c r="B229" s="4"/>
+      <c r="C229" s="4"/>
     </row>
     <row r="230">
-      <c r="C230" s="5"/>
+      <c r="C230" s="4"/>
     </row>
     <row r="231">
-      <c r="A231"/>
-      <c r="B231" s="5"/>
+      <c r="B231" s="4"/>
     </row>
     <row r="232">
-      <c r="A232"/>
-      <c r="B232" s="5"/>
+      <c r="B232" s="4"/>
     </row>
     <row r="233">
-      <c r="C233" s="5"/>
+      <c r="C233" s="4"/>
     </row>
     <row r="234">
-      <c r="A234"/>
-      <c r="B234" s="5"/>
+      <c r="B234" s="4"/>
     </row>
     <row r="235">
-      <c r="A235"/>
-      <c r="B235" s="5"/>
+      <c r="B235" s="4"/>
     </row>
     <row r="236">
-      <c r="B236" s="5"/>
-      <c r="C236" s="5"/>
+      <c r="B236" s="4"/>
+      <c r="C236" s="4"/>
     </row>
     <row r="237">
-      <c r="A237"/>
-      <c r="B237" s="5"/>
+      <c r="B237" s="4"/>
     </row>
     <row r="238">
-      <c r="A238"/>
-      <c r="B238" s="5"/>
+      <c r="B238" s="4"/>
     </row>
     <row r="239">
-      <c r="A239"/>
-      <c r="B239" s="5"/>
+      <c r="B239" s="4"/>
     </row>
     <row r="240">
-      <c r="A240"/>
-      <c r="B240" s="5"/>
+      <c r="B240" s="4"/>
     </row>
     <row r="241">
-      <c r="A241"/>
-      <c r="B241" s="5"/>
+      <c r="B241" s="4"/>
     </row>
     <row r="242">
-      <c r="A242"/>
-      <c r="B242" s="5"/>
+      <c r="B242" s="4"/>
     </row>
     <row r="243">
-      <c r="C243" s="5"/>
+      <c r="C243" s="4"/>
     </row>
     <row r="244">
-      <c r="A244"/>
-      <c r="B244" s="5"/>
+      <c r="B244" s="4"/>
     </row>
     <row r="245">
-      <c r="A245"/>
-      <c r="B245" s="5"/>
+      <c r="B245" s="4"/>
     </row>
     <row r="246">
-      <c r="C246" s="5"/>
+      <c r="C246" s="4"/>
     </row>
     <row r="247">
-      <c r="A247"/>
-      <c r="B247" s="5"/>
+      <c r="B247" s="4"/>
     </row>
     <row r="248">
-      <c r="A248"/>
-      <c r="B248" s="5"/>
+      <c r="B248" s="4"/>
     </row>
     <row r="249">
-      <c r="A249"/>
-      <c r="B249" s="5"/>
+      <c r="B249" s="4"/>
     </row>
     <row r="250">
-      <c r="C250" s="5"/>
+      <c r="C250" s="4"/>
     </row>
     <row r="251">
-      <c r="A251"/>
-      <c r="B251" s="5"/>
+      <c r="B251" s="4"/>
     </row>
     <row r="252">
-      <c r="C252" s="5"/>
+      <c r="C252" s="4"/>
     </row>
     <row r="253">
-      <c r="A253"/>
-      <c r="B253" s="5"/>
+      <c r="B253" s="4"/>
     </row>
     <row r="254">
-      <c r="A254"/>
-      <c r="B254" s="5"/>
+      <c r="B254" s="4"/>
     </row>
     <row r="255">
-      <c r="A255"/>
-      <c r="B255" s="5"/>
+      <c r="B255" s="4"/>
     </row>
     <row r="256">
-      <c r="A256"/>
-      <c r="B256" s="5"/>
+      <c r="B256" s="4"/>
     </row>
     <row r="257">
-      <c r="C257" s="5"/>
+      <c r="C257" s="4"/>
     </row>
     <row r="258">
-      <c r="A258"/>
-      <c r="B258" s="5"/>
-      <c r="D258"/>
-      <c r="E258"/>
+      <c r="B258" s="4"/>
     </row>
     <row r="259">
-      <c r="A259"/>
-      <c r="B259" s="5"/>
+      <c r="B259" s="4"/>
     </row>
     <row r="260">
-      <c r="A260"/>
-      <c r="B260" s="5"/>
+      <c r="B260" s="4"/>
     </row>
     <row r="261">
-      <c r="A261"/>
-      <c r="B261" s="5"/>
+      <c r="B261" s="4"/>
     </row>
     <row r="262">
-      <c r="A262"/>
-      <c r="B262" s="5"/>
+      <c r="B262" s="4"/>
     </row>
     <row r="263">
-      <c r="C263" s="5"/>
+      <c r="C263" s="4"/>
     </row>
     <row r="264">
-      <c r="A264"/>
-      <c r="B264" s="5"/>
+      <c r="B264" s="4"/>
     </row>
     <row r="265">
-      <c r="A265"/>
-      <c r="B265" s="5"/>
+      <c r="B265" s="4"/>
     </row>
     <row r="266">
-      <c r="A266"/>
-      <c r="B266" s="5"/>
+      <c r="B266" s="4"/>
     </row>
     <row r="267">
-      <c r="A267"/>
-      <c r="B267" s="5"/>
+      <c r="B267" s="4"/>
     </row>
     <row r="268">
-      <c r="C268" s="5"/>
+      <c r="C268" s="4"/>
     </row>
     <row r="269">
-      <c r="A269"/>
-      <c r="B269" s="5"/>
+      <c r="B269" s="4"/>
     </row>
     <row r="270">
-      <c r="A270"/>
-      <c r="B270" s="5"/>
+      <c r="B270" s="4"/>
     </row>
     <row r="271">
-      <c r="A271"/>
-      <c r="B271" s="5"/>
+      <c r="B271" s="4"/>
     </row>
     <row r="272">
-      <c r="A272"/>
-      <c r="B272" s="5"/>
+      <c r="B272" s="4"/>
     </row>
     <row r="273">
-      <c r="A273"/>
-      <c r="B273" s="5"/>
+      <c r="B273" s="4"/>
     </row>
     <row r="274">
-      <c r="A274"/>
-      <c r="B274" s="5"/>
+      <c r="B274" s="4"/>
     </row>
     <row r="275">
-      <c r="A275"/>
-      <c r="B275" s="5"/>
+      <c r="B275" s="4"/>
     </row>
     <row r="276">
-      <c r="A276"/>
-      <c r="B276" s="5"/>
+      <c r="B276" s="4"/>
     </row>
     <row r="277">
-      <c r="C277" s="5"/>
+      <c r="C277" s="4"/>
     </row>
     <row r="278">
-      <c r="A278"/>
-      <c r="B278" s="5"/>
+      <c r="B278" s="4"/>
     </row>
     <row r="279">
-      <c r="C279" s="5"/>
+      <c r="C279" s="4"/>
     </row>
     <row r="280">
-      <c r="A280"/>
-      <c r="B280" s="5"/>
+      <c r="B280" s="4"/>
     </row>
     <row r="281">
-      <c r="A281"/>
-      <c r="B281" s="5"/>
+      <c r="B281" s="4"/>
     </row>
     <row r="282">
-      <c r="A282"/>
-      <c r="B282" s="5"/>
+      <c r="B282" s="4"/>
     </row>
     <row r="283">
-      <c r="C283" s="5"/>
+      <c r="C283" s="4"/>
     </row>
     <row r="284">
-      <c r="C284" s="5"/>
+      <c r="C284" s="4"/>
     </row>
     <row r="285">
-      <c r="A285"/>
-      <c r="B285" s="5"/>
+      <c r="B285" s="4"/>
     </row>
     <row r="286">
-      <c r="A286"/>
-      <c r="B286" s="5"/>
+      <c r="B286" s="4"/>
     </row>
     <row r="287">
-      <c r="C287" s="5"/>
+      <c r="C287" s="4"/>
     </row>
     <row r="288">
-      <c r="A288"/>
-      <c r="B288" s="5"/>
+      <c r="B288" s="4"/>
     </row>
     <row r="289">
-      <c r="A289"/>
-      <c r="B289" s="5"/>
+      <c r="B289" s="4"/>
     </row>
     <row r="290">
-      <c r="A290"/>
-      <c r="B290" s="5"/>
+      <c r="B290" s="4"/>
     </row>
     <row r="291">
-      <c r="C291" s="5"/>
+      <c r="C291" s="4"/>
     </row>
     <row r="292">
-      <c r="A292"/>
-      <c r="B292" s="5"/>
+      <c r="B292" s="4"/>
     </row>
     <row r="293">
-      <c r="A293"/>
-      <c r="B293" s="5"/>
+      <c r="B293" s="4"/>
     </row>
     <row r="294">
-      <c r="A294"/>
-      <c r="B294" s="5"/>
+      <c r="B294" s="4"/>
     </row>
     <row r="295">
-      <c r="A295"/>
-      <c r="B295" s="5"/>
+      <c r="B295" s="4"/>
     </row>
     <row r="296">
-      <c r="C296" s="5"/>
+      <c r="C296" s="4"/>
     </row>
     <row r="297">
-      <c r="A297"/>
-      <c r="B297" s="5"/>
+      <c r="B297" s="4"/>
     </row>
     <row r="298">
-      <c r="A298"/>
-      <c r="B298" s="5"/>
+      <c r="B298" s="4"/>
     </row>
     <row r="299">
-      <c r="A299"/>
-      <c r="B299" s="5"/>
+      <c r="B299" s="4"/>
     </row>
     <row r="300">
-      <c r="A300"/>
-      <c r="B300" s="5"/>
+      <c r="B300" s="4"/>
     </row>
     <row r="301">
-      <c r="A301"/>
-      <c r="B301" s="5"/>
+      <c r="B301" s="4"/>
     </row>
     <row r="302">
-      <c r="A302"/>
-      <c r="B302" s="5"/>
+      <c r="B302" s="4"/>
     </row>
     <row r="303">
-      <c r="A303"/>
-      <c r="B303" s="5"/>
+      <c r="B303" s="4"/>
     </row>
     <row r="304">
-      <c r="A304"/>
-      <c r="B304" s="5"/>
+      <c r="B304" s="4"/>
     </row>
     <row r="305">
-      <c r="A305"/>
-      <c r="B305" s="5"/>
+      <c r="B305" s="4"/>
     </row>
     <row r="306">
-      <c r="A306"/>
-      <c r="B306" s="5"/>
+      <c r="B306" s="4"/>
     </row>
     <row r="307">
-      <c r="C307" s="5"/>
+      <c r="C307" s="4"/>
     </row>
     <row r="308">
-      <c r="A308"/>
-      <c r="B308" s="5"/>
+      <c r="B308" s="4"/>
     </row>
     <row r="309">
-      <c r="C309" s="5"/>
+      <c r="C309" s="4"/>
     </row>
     <row r="310">
-      <c r="A310"/>
-      <c r="B310" s="5"/>
+      <c r="B310" s="4"/>
     </row>
     <row r="311">
-      <c r="A311"/>
-      <c r="B311" s="5"/>
+      <c r="B311" s="4"/>
     </row>
     <row r="312">
-      <c r="A312"/>
-      <c r="B312" s="5"/>
+      <c r="B312" s="4"/>
     </row>
     <row r="313">
-      <c r="A313"/>
-      <c r="B313" s="5"/>
+      <c r="B313" s="4"/>
     </row>
     <row r="314">
-      <c r="C314" s="5"/>
+      <c r="C314" s="4"/>
     </row>
     <row r="315">
-      <c r="C315" s="5"/>
+      <c r="C315" s="4"/>
     </row>
     <row r="316">
-      <c r="A316"/>
-      <c r="B316" s="5"/>
+      <c r="B316" s="4"/>
     </row>
     <row r="317">
-      <c r="A317"/>
-      <c r="B317" s="5"/>
+      <c r="B317" s="4"/>
     </row>
     <row r="318">
-      <c r="A318"/>
-      <c r="B318" s="5"/>
+      <c r="B318" s="4"/>
     </row>
     <row r="319">
-      <c r="A319"/>
-      <c r="B319" s="5"/>
+      <c r="B319" s="4"/>
     </row>
     <row r="320">
-      <c r="A320"/>
-      <c r="B320" s="5"/>
+      <c r="B320" s="4"/>
     </row>
     <row r="321">
-      <c r="A321"/>
-      <c r="B321" s="5"/>
+      <c r="B321" s="4"/>
     </row>
     <row r="322">
-      <c r="A322"/>
-      <c r="B322" s="5"/>
+      <c r="B322" s="4"/>
     </row>
     <row r="323">
-      <c r="C323" s="5"/>
+      <c r="C323" s="4"/>
     </row>
     <row r="324">
-      <c r="A324"/>
-      <c r="B324" s="5"/>
+      <c r="B324" s="4"/>
     </row>
     <row r="325">
-      <c r="C325" s="5"/>
+      <c r="C325" s="4"/>
     </row>
     <row r="326">
-      <c r="C326" s="5"/>
+      <c r="C326" s="4"/>
     </row>
     <row r="327">
-      <c r="A327"/>
-      <c r="B327" s="5"/>
+      <c r="B327" s="4"/>
     </row>
     <row r="328">
-      <c r="A328"/>
-      <c r="B328" s="5"/>
+      <c r="B328" s="4"/>
     </row>
     <row r="329">
-      <c r="C329" s="5"/>
+      <c r="C329" s="4"/>
     </row>
     <row r="330">
-      <c r="A330"/>
-      <c r="B330" s="5"/>
+      <c r="B330" s="4"/>
     </row>
     <row r="331">
-      <c r="C331" s="5"/>
+      <c r="C331" s="4"/>
     </row>
     <row r="332">
-      <c r="A332"/>
-      <c r="B332" s="5"/>
+      <c r="B332" s="4"/>
     </row>
     <row r="333">
-      <c r="A333"/>
-      <c r="B333" s="5"/>
+      <c r="B333" s="4"/>
     </row>
     <row r="334">
-      <c r="A334"/>
-      <c r="B334" s="5"/>
+      <c r="B334" s="4"/>
     </row>
     <row r="335">
-      <c r="A335"/>
-      <c r="B335" s="5"/>
+      <c r="B335" s="4"/>
     </row>
     <row r="336">
-      <c r="A336"/>
-      <c r="B336" s="5"/>
+      <c r="B336" s="4"/>
     </row>
     <row r="337">
-      <c r="A337"/>
-      <c r="B337" s="5"/>
+      <c r="B337" s="4"/>
     </row>
     <row r="338">
-      <c r="A338"/>
-      <c r="B338" s="5"/>
+      <c r="B338" s="4"/>
     </row>
     <row r="339">
-      <c r="C339" s="5"/>
+      <c r="C339" s="4"/>
     </row>
     <row r="340">
-      <c r="A340"/>
-      <c r="B340" s="5"/>
+      <c r="B340" s="4"/>
     </row>
     <row r="341">
-      <c r="A341"/>
-      <c r="B341" s="5"/>
+      <c r="B341" s="4"/>
     </row>
     <row r="342">
-      <c r="C342" s="5"/>
+      <c r="C342" s="4"/>
     </row>
     <row r="343">
-      <c r="C343" s="5"/>
+      <c r="C343" s="4"/>
     </row>
     <row r="344">
-      <c r="C344" s="5"/>
+      <c r="C344" s="4"/>
     </row>
   </sheetData>
 </worksheet>
